--- a/Tower_Light/Source Code/Tower_Light/Template.xlsx
+++ b/Tower_Light/Source Code/Tower_Light/Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzz\Documents\Visual Studio\Tower Light\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzz\source\repos\Tower_Light\Tower_Light\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E51BA7-BF91-4394-8765-7E3B45BCECB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E70EB3-7AB8-48D4-90DF-0D66BD8194A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{32AB67E4-ABDB-4072-A16F-9CFCCB8B581F}"/>
   </bookViews>
@@ -206,13 +206,13 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Cordia New"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Cordia New"/>
       <family val="2"/>
@@ -358,10 +358,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -388,35 +391,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1586,28 +1586,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
     </row>
     <row r="2" spans="1:20" ht="1.8" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="2"/>
@@ -1632,34 +1632,34 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="19" t="s">
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="20"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="22"/>
     </row>
     <row r="4" spans="1:20" ht="2.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="O4" s="9"/>
@@ -1669,192 +1669,192 @@
       <c r="S4" s="9"/>
       <c r="T4" s="11"/>
     </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:20" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="22" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22" t="s">
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="24"/>
-    </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="28"/>
+    </row>
+    <row r="6" spans="1:20" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22" t="s">
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="24"/>
-    </row>
-    <row r="7" spans="1:20" s="7" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="28"/>
+    </row>
+    <row r="7" spans="1:20" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="23" t="s">
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="25"/>
-    </row>
-    <row r="8" spans="1:20" s="7" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="29"/>
+    </row>
+    <row r="8" spans="1:20" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="26" t="s">
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="27"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
     </row>
     <row r="9" spans="1:20" ht="19.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="23"/>
+      <c r="D9" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
+      <c r="G9" s="23"/>
+      <c r="H9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12" t="s">
+      <c r="I9" s="23"/>
+      <c r="J9" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12" t="s">
+      <c r="K9" s="23"/>
+      <c r="L9" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12" t="s">
+      <c r="M9" s="23"/>
+      <c r="N9" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="O9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="P9" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="Q9" s="12" t="s">
+      <c r="Q9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="R9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="S9" s="14"/>
-      <c r="T9" s="13" t="s">
+      <c r="S9" s="15"/>
+      <c r="T9" s="24" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="19.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="13"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="13" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="S10" s="13" t="s">
+      <c r="S10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="T10" s="13"/>
+      <c r="T10" s="24"/>
     </row>
     <row r="11" spans="1:20" ht="19.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="13"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
@@ -1891,13 +1891,13 @@
       <c r="M11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
     </row>
     <row r="12" spans="1:20" s="7" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -3330,172 +3330,158 @@
       <c r="T76" s="8"/>
     </row>
     <row r="77" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A77" s="28"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="29"/>
-      <c r="J77" s="29"/>
-      <c r="K77" s="29"/>
-      <c r="L77" s="29"/>
-      <c r="M77" s="29"/>
-      <c r="N77" s="29"/>
-      <c r="O77" s="29"/>
-      <c r="P77" s="29"/>
-      <c r="Q77" s="29"/>
-      <c r="R77" s="29"/>
-      <c r="S77" s="29"/>
-      <c r="T77" s="29"/>
+      <c r="A77" s="12"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="13"/>
+      <c r="L77" s="13"/>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13"/>
+      <c r="P77" s="13"/>
+      <c r="Q77" s="13"/>
+      <c r="R77" s="13"/>
+      <c r="S77" s="13"/>
+      <c r="T77" s="13"/>
     </row>
     <row r="78" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A78" s="28"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
-      <c r="F78" s="29"/>
-      <c r="G78" s="29"/>
-      <c r="H78" s="29"/>
-      <c r="I78" s="29"/>
-      <c r="J78" s="29"/>
-      <c r="K78" s="29"/>
-      <c r="L78" s="29"/>
-      <c r="M78" s="29"/>
-      <c r="N78" s="29"/>
-      <c r="O78" s="29"/>
-      <c r="P78" s="29"/>
-      <c r="Q78" s="29"/>
-      <c r="R78" s="29"/>
-      <c r="S78" s="29"/>
-      <c r="T78" s="29"/>
+      <c r="A78" s="12"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13"/>
+      <c r="P78" s="13"/>
+      <c r="Q78" s="13"/>
+      <c r="R78" s="13"/>
+      <c r="S78" s="13"/>
+      <c r="T78" s="13"/>
     </row>
     <row r="79" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A79" s="28"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
-      <c r="F79" s="29"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="29"/>
-      <c r="J79" s="29"/>
-      <c r="K79" s="29"/>
-      <c r="L79" s="29"/>
-      <c r="M79" s="29"/>
-      <c r="N79" s="29"/>
-      <c r="O79" s="29"/>
-      <c r="P79" s="29"/>
-      <c r="Q79" s="29"/>
-      <c r="R79" s="29"/>
-      <c r="S79" s="29"/>
-      <c r="T79" s="29"/>
+      <c r="A79" s="12"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I79" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="J79" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K79" s="14"/>
+      <c r="L79" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M79" s="25"/>
+      <c r="N79" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="O79" s="25"/>
+      <c r="P79" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q79" s="25"/>
+      <c r="R79" s="14"/>
+      <c r="S79" s="14"/>
+      <c r="T79" s="14"/>
     </row>
     <row r="80" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A80" s="28"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="29"/>
-      <c r="F80" s="29"/>
-      <c r="G80" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="H80" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="I80" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="J80" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="K80" s="31"/>
-      <c r="L80" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="M80" s="30"/>
-      <c r="N80" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="O80" s="30"/>
-      <c r="P80" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q80" s="30"/>
-      <c r="R80" s="31"/>
-      <c r="S80" s="31"/>
-      <c r="T80" s="31"/>
+      <c r="A80" s="12"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="25"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="25"/>
+      <c r="M80" s="25"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="25"/>
+      <c r="P80" s="25"/>
+      <c r="Q80" s="25"/>
+      <c r="R80" s="14"/>
+      <c r="S80" s="14"/>
+      <c r="T80" s="14"/>
     </row>
     <row r="81" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A81" s="28"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="29"/>
-      <c r="F81" s="29"/>
-      <c r="G81" s="30"/>
-      <c r="H81" s="30"/>
-      <c r="I81" s="30"/>
-      <c r="J81" s="30"/>
-      <c r="K81" s="31"/>
-      <c r="L81" s="30"/>
-      <c r="M81" s="30"/>
-      <c r="N81" s="30"/>
-      <c r="O81" s="30"/>
-      <c r="P81" s="30"/>
-      <c r="Q81" s="30"/>
-      <c r="R81" s="31"/>
-      <c r="S81" s="31"/>
-      <c r="T81" s="31"/>
+      <c r="A81" s="12"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="19"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="19"/>
+      <c r="M81" s="19"/>
+      <c r="N81" s="19"/>
+      <c r="O81" s="19"/>
+      <c r="P81" s="19"/>
+      <c r="Q81" s="19"/>
+      <c r="R81" s="19"/>
+      <c r="S81" s="19"/>
+      <c r="T81" s="19"/>
     </row>
     <row r="82" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A82" s="31"/>
-      <c r="B82" s="31"/>
-      <c r="C82" s="31"/>
-      <c r="D82" s="31"/>
-      <c r="E82" s="31"/>
-      <c r="F82" s="31"/>
-      <c r="G82" s="18"/>
-      <c r="H82" s="18"/>
-      <c r="I82" s="18"/>
-      <c r="J82" s="18"/>
-      <c r="K82" s="31"/>
-      <c r="L82" s="18"/>
-      <c r="M82" s="18"/>
-      <c r="N82" s="18"/>
-      <c r="O82" s="18"/>
-      <c r="P82" s="18"/>
-      <c r="Q82" s="18"/>
-      <c r="R82" s="18"/>
-      <c r="S82" s="18"/>
-      <c r="T82" s="18"/>
+      <c r="A82" s="14"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="19"/>
+      <c r="M82" s="19"/>
+      <c r="N82" s="19"/>
+      <c r="O82" s="19"/>
+      <c r="P82" s="19"/>
+      <c r="Q82" s="19"/>
+      <c r="R82" s="19"/>
+      <c r="S82" s="19"/>
+      <c r="T82" s="19"/>
     </row>
     <row r="83" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A83" s="31"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="31"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="18"/>
-      <c r="H83" s="18"/>
-      <c r="I83" s="18"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="31"/>
-      <c r="L83" s="18"/>
-      <c r="M83" s="18"/>
-      <c r="N83" s="18"/>
-      <c r="O83" s="18"/>
-      <c r="P83" s="18"/>
-      <c r="Q83" s="18"/>
-      <c r="R83" s="18"/>
-      <c r="S83" s="18"/>
-      <c r="T83" s="18"/>
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
     </row>
     <row r="84" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6"/>
     <row r="85" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6"/>
@@ -3505,18 +3491,26 @@
     <row r="89" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="O3:T3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="P81:Q82"/>
+    <mergeCell ref="R81:T82"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="J81:J82"/>
+    <mergeCell ref="L81:M82"/>
+    <mergeCell ref="N81:O82"/>
+    <mergeCell ref="N79:O80"/>
+    <mergeCell ref="P79:Q80"/>
+    <mergeCell ref="L9:M10"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="G79:G80"/>
+    <mergeCell ref="H79:H80"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="J79:J80"/>
+    <mergeCell ref="L79:M80"/>
     <mergeCell ref="J9:K10"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="H7:N7"/>
@@ -3533,26 +3527,18 @@
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="S10:S11"/>
     <mergeCell ref="R9:S9"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="L80:M81"/>
-    <mergeCell ref="N80:O81"/>
-    <mergeCell ref="P80:Q81"/>
-    <mergeCell ref="L9:M10"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="P82:Q83"/>
-    <mergeCell ref="R82:T83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="L82:M83"/>
-    <mergeCell ref="N82:O83"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="portrait" r:id="rId1"/>
